--- a/data_lake/datos_diarios_preliminares/dt=2026-07-24/Temp-max-julio-26.xlsx
+++ b/data_lake/datos_diarios_preliminares/dt=2026-07-24/Temp-max-julio-26.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\02. Datos Diarios\Tablas\Datos hidrometeorologicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C1012F-4726-49C1-B0A2-152DD34EE689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7BC1130-FC5B-4D48-BBBE-BD2DC52E05A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9490,7 +9490,9 @@
       <c r="Z5" s="57">
         <v>30.7</v>
       </c>
-      <c r="AA5" s="57"/>
+      <c r="AA5" s="57">
+        <v>31.2</v>
+      </c>
       <c r="AB5" s="57"/>
       <c r="AC5" s="57"/>
       <c r="AD5" s="57"/>
@@ -9501,7 +9503,7 @@
       <c r="AI5" s="57"/>
       <c r="AJ5" s="37">
         <f>+IF(SUM($E5:$AI5)&gt;0,LOOKUP(1000,$E5:$AI5),NA())</f>
-        <v>30.7</v>
+        <v>31.2</v>
       </c>
       <c r="AK5" s="21">
         <f>+MAX($E5:$AI5)</f>
@@ -9519,11 +9521,11 @@
       </c>
       <c r="AO5" s="23">
         <f>IF(COUNTIF(E5:AI5,"&gt;0")&gt;=15,AVERAGE(E5:AI5),"")</f>
-        <v>31.059090909090912</v>
+        <v>31.065217391304351</v>
       </c>
       <c r="AP5" s="23">
         <f>IF(AN5&gt;0,IFERROR(AO5-AN5,""),"")</f>
-        <v>0.86171913308268344</v>
+        <v>0.86784561529612247</v>
       </c>
     </row>
     <row r="6" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9605,7 +9607,9 @@
       <c r="Z6" s="57">
         <v>31.1</v>
       </c>
-      <c r="AA6" s="57"/>
+      <c r="AA6" s="57">
+        <v>30.8</v>
+      </c>
       <c r="AB6" s="57"/>
       <c r="AC6" s="57"/>
       <c r="AD6" s="57"/>
@@ -9616,7 +9620,7 @@
       <c r="AI6" s="57"/>
       <c r="AJ6" s="37">
         <f t="shared" ref="AJ6:AJ48" si="0">+IF(SUM($E6:$AI6)&gt;0,LOOKUP(1000,$E6:$AI6),NA())</f>
-        <v>31.1</v>
+        <v>30.8</v>
       </c>
       <c r="AK6" s="21">
         <f t="shared" ref="AK6:AK48" si="1">+MAX($E6:$AI6)</f>
@@ -9634,11 +9638,11 @@
       </c>
       <c r="AO6" s="23">
         <f t="shared" ref="AO6:AO15" si="3">IF(COUNTIF(E6:AI6,"&gt;0")&gt;=15,AVERAGE(E6:AI6),"")</f>
-        <v>30.645454545454541</v>
+        <v>30.652173913043473</v>
       </c>
       <c r="AP6" s="23">
         <f t="shared" ref="AP6:AP48" si="4">IF(AN6&gt;0,IFERROR(AO6-AN6,""),"")</f>
-        <v>-8.8258515677992477E-3</v>
+        <v>-2.1064839788671463E-3</v>
       </c>
     </row>
     <row r="7" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9720,7 +9724,9 @@
       <c r="Z7" s="57">
         <v>35</v>
       </c>
-      <c r="AA7" s="57"/>
+      <c r="AA7" s="57">
+        <v>32</v>
+      </c>
       <c r="AB7" s="57"/>
       <c r="AC7" s="57"/>
       <c r="AD7" s="57"/>
@@ -9731,7 +9737,7 @@
       <c r="AI7" s="57"/>
       <c r="AJ7" s="37">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="AK7" s="21">
         <f t="shared" si="1"/>
@@ -9749,11 +9755,11 @@
       </c>
       <c r="AO7" s="23">
         <f t="shared" si="3"/>
-        <v>35.699999999999996</v>
+        <v>35.539130434782606</v>
       </c>
       <c r="AP7" s="23">
         <f t="shared" si="4"/>
-        <v>2.3339839924309231</v>
+        <v>2.1731144272135339</v>
       </c>
     </row>
     <row r="8" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9835,7 +9841,9 @@
       <c r="Z8" s="57">
         <v>33.1</v>
       </c>
-      <c r="AA8" s="57"/>
+      <c r="AA8" s="57">
+        <v>32.4</v>
+      </c>
       <c r="AB8" s="57"/>
       <c r="AC8" s="57"/>
       <c r="AD8" s="57"/>
@@ -9846,7 +9854,7 @@
       <c r="AI8" s="57"/>
       <c r="AJ8" s="37">
         <f t="shared" si="0"/>
-        <v>33.1</v>
+        <v>32.4</v>
       </c>
       <c r="AK8" s="21">
         <f t="shared" si="1"/>
@@ -9864,11 +9872,11 @@
       </c>
       <c r="AO8" s="23">
         <f t="shared" si="3"/>
-        <v>33.240909090909092</v>
+        <v>33.204347826086959</v>
       </c>
       <c r="AP8" s="23">
         <f t="shared" si="4"/>
-        <v>0.99186608015639877</v>
+        <v>0.95530481533426581</v>
       </c>
     </row>
     <row r="9" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9950,7 +9958,9 @@
       <c r="Z9" s="57">
         <v>33.6</v>
       </c>
-      <c r="AA9" s="57"/>
+      <c r="AA9" s="57">
+        <v>33.799999999999997</v>
+      </c>
       <c r="AB9" s="57"/>
       <c r="AC9" s="57"/>
       <c r="AD9" s="57"/>
@@ -9961,7 +9971,7 @@
       <c r="AI9" s="57"/>
       <c r="AJ9" s="37">
         <f t="shared" si="0"/>
-        <v>33.6</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="AK9" s="21">
         <f t="shared" si="1"/>
@@ -9979,11 +9989,11 @@
       </c>
       <c r="AO9" s="23">
         <f t="shared" si="3"/>
-        <v>33.777272727272731</v>
+        <v>33.778260869565216</v>
       </c>
       <c r="AP9" s="23">
         <f t="shared" si="4"/>
-        <v>0.68602658958888441</v>
+        <v>0.6870147318813693</v>
       </c>
     </row>
     <row r="10" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10065,7 +10075,9 @@
       <c r="Z10" s="57">
         <v>35.5</v>
       </c>
-      <c r="AA10" s="57"/>
+      <c r="AA10" s="57">
+        <v>36</v>
+      </c>
       <c r="AB10" s="57"/>
       <c r="AC10" s="57"/>
       <c r="AD10" s="57"/>
@@ -10076,7 +10088,7 @@
       <c r="AI10" s="57"/>
       <c r="AJ10" s="37">
         <f t="shared" si="0"/>
-        <v>35.5</v>
+        <v>36</v>
       </c>
       <c r="AK10" s="21">
         <f t="shared" si="1"/>
@@ -10094,11 +10106,11 @@
       </c>
       <c r="AO10" s="23">
         <f t="shared" si="3"/>
-        <v>35.772727272727266</v>
+        <v>35.782608695652172</v>
       </c>
       <c r="AP10" s="23">
         <f t="shared" si="4"/>
-        <v>0.39248904506690963</v>
+        <v>0.40237046799181542</v>
       </c>
     </row>
     <row r="11" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10180,7 +10192,9 @@
       <c r="Z11" s="57">
         <v>37.700000000000003</v>
       </c>
-      <c r="AA11" s="57"/>
+      <c r="AA11" s="57">
+        <v>34</v>
+      </c>
       <c r="AB11" s="57"/>
       <c r="AC11" s="57"/>
       <c r="AD11" s="57"/>
@@ -10191,7 +10205,7 @@
       <c r="AI11" s="57"/>
       <c r="AJ11" s="37">
         <f t="shared" si="0"/>
-        <v>37.700000000000003</v>
+        <v>34</v>
       </c>
       <c r="AK11" s="21">
         <f t="shared" si="1"/>
@@ -10209,11 +10223,11 @@
       </c>
       <c r="AO11" s="23">
         <f t="shared" si="3"/>
-        <v>38.127272727272718</v>
+        <v>37.947826086956518</v>
       </c>
       <c r="AP11" s="23">
         <f t="shared" si="4"/>
-        <v>2.5899886344241168</v>
+        <v>2.4105419941079163</v>
       </c>
     </row>
     <row r="12" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10295,7 +10309,9 @@
       <c r="Z12" s="57">
         <v>34.200000000000003</v>
       </c>
-      <c r="AA12" s="57"/>
+      <c r="AA12" s="57">
+        <v>36.799999999999997</v>
+      </c>
       <c r="AB12" s="57"/>
       <c r="AC12" s="57"/>
       <c r="AD12" s="57"/>
@@ -10306,7 +10322,7 @@
       <c r="AI12" s="57"/>
       <c r="AJ12" s="37">
         <f t="shared" si="0"/>
-        <v>34.200000000000003</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="AK12" s="21">
         <f t="shared" si="1"/>
@@ -10324,11 +10340,11 @@
       </c>
       <c r="AO12" s="23">
         <f t="shared" si="3"/>
-        <v>34.654545454545456</v>
+        <v>34.747826086956522</v>
       </c>
       <c r="AP12" s="23">
         <f t="shared" si="4"/>
-        <v>2.4659213083717191</v>
+        <v>2.5592019407827848</v>
       </c>
     </row>
     <row r="13" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10410,7 +10426,9 @@
       <c r="Z13" s="57">
         <v>35</v>
       </c>
-      <c r="AA13" s="57"/>
+      <c r="AA13" s="57">
+        <v>27.6</v>
+      </c>
       <c r="AB13" s="57"/>
       <c r="AC13" s="57"/>
       <c r="AD13" s="57"/>
@@ -10421,7 +10439,7 @@
       <c r="AI13" s="57"/>
       <c r="AJ13" s="37">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>27.6</v>
       </c>
       <c r="AK13" s="21">
         <f t="shared" si="1"/>
@@ -10439,11 +10457,11 @@
       </c>
       <c r="AO13" s="23">
         <f t="shared" si="3"/>
-        <v>35.81818181818182</v>
+        <v>35.460869565217394</v>
       </c>
       <c r="AP13" s="23">
         <f t="shared" si="4"/>
-        <v>2.4363897034864834</v>
+        <v>2.0790774505220568</v>
       </c>
     </row>
     <row r="14" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10525,7 +10543,9 @@
       <c r="Z14" s="57">
         <v>35.9</v>
       </c>
-      <c r="AA14" s="57"/>
+      <c r="AA14" s="57">
+        <v>26.2</v>
+      </c>
       <c r="AB14" s="57"/>
       <c r="AC14" s="57"/>
       <c r="AD14" s="57"/>
@@ -10536,7 +10556,7 @@
       <c r="AI14" s="57"/>
       <c r="AJ14" s="37">
         <f t="shared" si="0"/>
-        <v>35.9</v>
+        <v>26.2</v>
       </c>
       <c r="AK14" s="21">
         <f t="shared" si="1"/>
@@ -10554,11 +10574,11 @@
       </c>
       <c r="AO14" s="23">
         <f t="shared" si="3"/>
-        <v>35.081818181818178</v>
+        <v>34.695652173913047</v>
       </c>
       <c r="AP14" s="23">
         <f t="shared" si="4"/>
-        <v>1.8568815826039469</v>
+        <v>1.470715574698815</v>
       </c>
     </row>
     <row r="15" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10640,7 +10660,9 @@
       <c r="Z15" s="57">
         <v>32.799999999999997</v>
       </c>
-      <c r="AA15" s="57"/>
+      <c r="AA15" s="57">
+        <v>27.9</v>
+      </c>
       <c r="AB15" s="57"/>
       <c r="AC15" s="57"/>
       <c r="AD15" s="57"/>
@@ -10651,7 +10673,7 @@
       <c r="AI15" s="57"/>
       <c r="AJ15" s="37">
         <f t="shared" si="0"/>
-        <v>32.799999999999997</v>
+        <v>27.9</v>
       </c>
       <c r="AK15" s="21">
         <f t="shared" si="1"/>
@@ -10669,11 +10691,11 @@
       </c>
       <c r="AO15" s="23">
         <f t="shared" si="3"/>
-        <v>31.868181818181814</v>
+        <v>31.695652173913039</v>
       </c>
       <c r="AP15" s="23">
         <f t="shared" si="4"/>
-        <v>0.13284436210186357</v>
+        <v>-3.9685282166910696E-2</v>
       </c>
     </row>
     <row r="16" spans="1:46" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10804,7 +10826,9 @@
       <c r="Z17" s="57">
         <v>34.4</v>
       </c>
-      <c r="AA17" s="57"/>
+      <c r="AA17" s="57">
+        <v>30.5</v>
+      </c>
       <c r="AB17" s="57"/>
       <c r="AC17" s="57"/>
       <c r="AD17" s="57"/>
@@ -10815,7 +10839,7 @@
       <c r="AI17" s="57"/>
       <c r="AJ17" s="37">
         <f t="shared" si="0"/>
-        <v>34.4</v>
+        <v>30.5</v>
       </c>
       <c r="AK17" s="21">
         <f t="shared" si="1"/>
@@ -10833,11 +10857,11 @@
       </c>
       <c r="AO17" s="23">
         <f>IF(COUNTIF(E17:AI17,"&gt;0")&gt;=15,AVERAGE(E17:AI17),"")</f>
-        <v>34.309090909090905</v>
+        <v>34.143478260869557</v>
       </c>
       <c r="AP17" s="23">
         <f>IF(AN17&gt;0,IFERROR(AO17-AN17,""),"")</f>
-        <v>1.6351087066437486</v>
+        <v>1.4694960584224006</v>
       </c>
     </row>
     <row r="18" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10919,7 +10943,9 @@
       <c r="Z18" s="57">
         <v>28.6</v>
       </c>
-      <c r="AA18" s="57"/>
+      <c r="AA18" s="57">
+        <v>26.7</v>
+      </c>
       <c r="AB18" s="57"/>
       <c r="AC18" s="57"/>
       <c r="AD18" s="57"/>
@@ -10930,7 +10956,7 @@
       <c r="AI18" s="57"/>
       <c r="AJ18" s="37">
         <f t="shared" si="0"/>
-        <v>28.6</v>
+        <v>26.7</v>
       </c>
       <c r="AK18" s="21">
         <f t="shared" si="1"/>
@@ -10948,11 +10974,11 @@
       </c>
       <c r="AO18" s="23">
         <f t="shared" ref="AO18:AO33" si="5">IF(COUNTIF(E18:AI18,"&gt;0")&gt;=15,AVERAGE(E18:AI18),"")</f>
-        <v>27.90454545454546</v>
+        <v>27.852173913043483</v>
       </c>
       <c r="AP18" s="23">
         <f t="shared" si="4"/>
-        <v>1.8446746005885899</v>
+        <v>1.7923030590866134</v>
       </c>
     </row>
     <row r="19" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11034,7 +11060,9 @@
       <c r="Z19" s="57">
         <v>36.4</v>
       </c>
-      <c r="AA19" s="57"/>
+      <c r="AA19" s="57">
+        <v>31.3</v>
+      </c>
       <c r="AB19" s="57"/>
       <c r="AC19" s="57"/>
       <c r="AD19" s="57"/>
@@ -11045,7 +11073,7 @@
       <c r="AI19" s="57"/>
       <c r="AJ19" s="37">
         <f t="shared" si="0"/>
-        <v>36.4</v>
+        <v>31.3</v>
       </c>
       <c r="AK19" s="21">
         <f t="shared" si="1"/>
@@ -11063,11 +11091,11 @@
       </c>
       <c r="AO19" s="23">
         <f t="shared" si="5"/>
-        <v>33.718181818181819</v>
+        <v>33.613043478260863</v>
       </c>
       <c r="AP19" s="23">
         <f t="shared" si="4"/>
-        <v>0.46721941551217583</v>
+        <v>0.36208107559122027</v>
       </c>
     </row>
     <row r="20" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11149,7 +11177,9 @@
       <c r="Z20" s="57">
         <v>28.6</v>
       </c>
-      <c r="AA20" s="57"/>
+      <c r="AA20" s="57">
+        <v>27</v>
+      </c>
       <c r="AB20" s="57"/>
       <c r="AC20" s="57"/>
       <c r="AD20" s="57"/>
@@ -11160,7 +11190,7 @@
       <c r="AI20" s="57"/>
       <c r="AJ20" s="37">
         <f t="shared" si="0"/>
-        <v>28.6</v>
+        <v>27</v>
       </c>
       <c r="AK20" s="21">
         <f t="shared" si="1"/>
@@ -11178,11 +11208,11 @@
       </c>
       <c r="AO20" s="23">
         <f t="shared" si="5"/>
-        <v>30.340909090909097</v>
+        <v>30.19565217391305</v>
       </c>
       <c r="AP20" s="23">
         <f t="shared" si="4"/>
-        <v>1.7001044932079488</v>
+        <v>1.5548475762119018</v>
       </c>
     </row>
     <row r="21" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11264,7 +11294,9 @@
       <c r="Z21" s="57">
         <v>25.3</v>
       </c>
-      <c r="AA21" s="57"/>
+      <c r="AA21" s="57">
+        <v>23.4</v>
+      </c>
       <c r="AB21" s="57"/>
       <c r="AC21" s="57"/>
       <c r="AD21" s="57"/>
@@ -11275,7 +11307,7 @@
       <c r="AI21" s="57"/>
       <c r="AJ21" s="37">
         <f t="shared" si="0"/>
-        <v>25.3</v>
+        <v>23.4</v>
       </c>
       <c r="AK21" s="21">
         <f t="shared" si="1"/>
@@ -11293,11 +11325,11 @@
       </c>
       <c r="AO21" s="23">
         <f t="shared" si="5"/>
-        <v>24.340909090909086</v>
+        <v>24.299999999999994</v>
       </c>
       <c r="AP21" s="23">
         <f t="shared" si="4"/>
-        <v>1.7314059392591155</v>
+        <v>1.6904968483500227</v>
       </c>
     </row>
     <row r="22" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11447,7 +11479,9 @@
       <c r="Z23" s="57">
         <v>29.9</v>
       </c>
-      <c r="AA23" s="57"/>
+      <c r="AA23" s="57">
+        <v>25.8</v>
+      </c>
       <c r="AB23" s="57"/>
       <c r="AC23" s="57"/>
       <c r="AD23" s="57"/>
@@ -11458,7 +11492,7 @@
       <c r="AI23" s="57"/>
       <c r="AJ23" s="37">
         <f t="shared" si="0"/>
-        <v>29.9</v>
+        <v>25.8</v>
       </c>
       <c r="AK23" s="21">
         <f t="shared" si="1"/>
@@ -11476,11 +11510,11 @@
       </c>
       <c r="AO23" s="23">
         <f t="shared" si="5"/>
-        <v>28.727272727272734</v>
+        <v>28.6</v>
       </c>
       <c r="AP23" s="23">
         <f t="shared" si="4"/>
-        <v>1.8588856304985342</v>
+        <v>1.7316129032258019</v>
       </c>
     </row>
     <row r="24" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11562,7 +11596,9 @@
       <c r="Z24" s="57">
         <v>29.8</v>
       </c>
-      <c r="AA24" s="57"/>
+      <c r="AA24" s="57">
+        <v>27.7</v>
+      </c>
       <c r="AB24" s="57"/>
       <c r="AC24" s="57"/>
       <c r="AD24" s="57"/>
@@ -11573,7 +11609,7 @@
       <c r="AI24" s="57"/>
       <c r="AJ24" s="37">
         <f t="shared" si="0"/>
-        <v>29.8</v>
+        <v>27.7</v>
       </c>
       <c r="AK24" s="21">
         <f t="shared" si="1"/>
@@ -11591,11 +11627,11 @@
       </c>
       <c r="AO24" s="23">
         <f t="shared" si="5"/>
-        <v>29.636363636363637</v>
+        <v>29.552173913043479</v>
       </c>
       <c r="AP24" s="23">
         <f t="shared" si="4"/>
-        <v>1.3845395196201551</v>
+        <v>1.3003497962999973</v>
       </c>
     </row>
     <row r="25" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11677,7 +11713,9 @@
       <c r="Z25" s="57">
         <v>34.1</v>
       </c>
-      <c r="AA25" s="57"/>
+      <c r="AA25" s="57">
+        <v>32.200000000000003</v>
+      </c>
       <c r="AB25" s="57"/>
       <c r="AC25" s="57"/>
       <c r="AD25" s="57"/>
@@ -11688,7 +11726,7 @@
       <c r="AI25" s="57"/>
       <c r="AJ25" s="37">
         <f t="shared" si="0"/>
-        <v>34.1</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="AK25" s="21">
         <f t="shared" si="1"/>
@@ -11706,11 +11744,11 @@
       </c>
       <c r="AO25" s="23">
         <f t="shared" si="5"/>
-        <v>32.363636363636367</v>
+        <v>32.356521739130443</v>
       </c>
       <c r="AP25" s="23">
         <f t="shared" si="4"/>
-        <v>1.9877709704152977</v>
+        <v>1.9806563459093738</v>
       </c>
     </row>
     <row r="26" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11792,7 +11830,9 @@
       <c r="Z26" s="57">
         <v>20.7</v>
       </c>
-      <c r="AA26" s="57"/>
+      <c r="AA26" s="57">
+        <v>19.2</v>
+      </c>
       <c r="AB26" s="57"/>
       <c r="AC26" s="57"/>
       <c r="AD26" s="57"/>
@@ -11803,7 +11843,7 @@
       <c r="AI26" s="57"/>
       <c r="AJ26" s="37">
         <f t="shared" si="0"/>
-        <v>20.7</v>
+        <v>19.2</v>
       </c>
       <c r="AK26" s="21">
         <f t="shared" si="1"/>
@@ -11821,11 +11861,11 @@
       </c>
       <c r="AO26" s="23">
         <f t="shared" si="5"/>
-        <v>19.72727272727273</v>
+        <v>19.704347826086959</v>
       </c>
       <c r="AP26" s="23">
         <f t="shared" si="4"/>
-        <v>1.1844011198293707</v>
+        <v>1.1614762186435996</v>
       </c>
     </row>
     <row r="27" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11907,7 +11947,9 @@
       <c r="Z27" s="57">
         <v>21.2</v>
       </c>
-      <c r="AA27" s="57"/>
+      <c r="AA27" s="57">
+        <v>18</v>
+      </c>
       <c r="AB27" s="57"/>
       <c r="AC27" s="57"/>
       <c r="AD27" s="57"/>
@@ -11918,7 +11960,7 @@
       <c r="AI27" s="57"/>
       <c r="AJ27" s="37">
         <f t="shared" si="0"/>
-        <v>21.2</v>
+        <v>18</v>
       </c>
       <c r="AK27" s="21">
         <f t="shared" si="1"/>
@@ -11936,11 +11978,11 @@
       </c>
       <c r="AO27" s="23">
         <f t="shared" si="5"/>
-        <v>18.831818181818178</v>
+        <v>18.795652173913041</v>
       </c>
       <c r="AP27" s="23">
         <f t="shared" si="4"/>
-        <v>2.1497676377097896</v>
+        <v>2.113601629804652</v>
       </c>
     </row>
     <row r="28" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12022,7 +12064,9 @@
       <c r="Z28" s="57">
         <v>33.6</v>
       </c>
-      <c r="AA28" s="57"/>
+      <c r="AA28" s="57">
+        <v>30.8</v>
+      </c>
       <c r="AB28" s="57"/>
       <c r="AC28" s="57"/>
       <c r="AD28" s="57"/>
@@ -12033,7 +12077,7 @@
       <c r="AI28" s="57"/>
       <c r="AJ28" s="37">
         <f t="shared" si="0"/>
-        <v>33.6</v>
+        <v>30.8</v>
       </c>
       <c r="AK28" s="21">
         <f t="shared" si="1"/>
@@ -12051,11 +12095,11 @@
       </c>
       <c r="AO28" s="23">
         <f t="shared" si="5"/>
-        <v>31.981818181818188</v>
+        <v>31.9304347826087</v>
       </c>
       <c r="AP28" s="23">
         <f t="shared" si="4"/>
-        <v>1.4533655801620284</v>
+        <v>1.4019821809525403</v>
       </c>
     </row>
     <row r="29" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12203,7 +12247,9 @@
       <c r="Z30" s="57">
         <v>36</v>
       </c>
-      <c r="AA30" s="57"/>
+      <c r="AA30" s="57">
+        <v>34.700000000000003</v>
+      </c>
       <c r="AB30" s="57"/>
       <c r="AC30" s="57"/>
       <c r="AD30" s="57"/>
@@ -12214,7 +12260,7 @@
       <c r="AI30" s="57"/>
       <c r="AJ30" s="37">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="AK30" s="21">
         <f t="shared" si="1"/>
@@ -12232,11 +12278,11 @@
       </c>
       <c r="AO30" s="23">
         <f t="shared" si="5"/>
-        <v>34.695454545454545</v>
+        <v>34.695652173913047</v>
       </c>
       <c r="AP30" s="23">
         <f t="shared" si="4"/>
-        <v>0.95320364939719582</v>
+        <v>0.95340127785569706</v>
       </c>
     </row>
     <row r="31" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12318,7 +12364,9 @@
       <c r="Z31" s="57">
         <v>29.1</v>
       </c>
-      <c r="AA31" s="57"/>
+      <c r="AA31" s="57">
+        <v>25.3</v>
+      </c>
       <c r="AB31" s="57"/>
       <c r="AC31" s="57"/>
       <c r="AD31" s="57"/>
@@ -12329,7 +12377,7 @@
       <c r="AI31" s="57"/>
       <c r="AJ31" s="37">
         <f t="shared" si="0"/>
-        <v>29.1</v>
+        <v>25.3</v>
       </c>
       <c r="AK31" s="21">
         <f t="shared" si="1"/>
@@ -12347,11 +12395,11 @@
       </c>
       <c r="AO31" s="23">
         <f t="shared" si="5"/>
-        <v>27.372727272727271</v>
+        <v>27.282608695652169</v>
       </c>
       <c r="AP31" s="23">
         <f t="shared" si="4"/>
-        <v>1.985302435606652</v>
+        <v>1.8951838585315492</v>
       </c>
     </row>
     <row r="32" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12433,7 +12481,9 @@
       <c r="Z32" s="57">
         <v>20</v>
       </c>
-      <c r="AA32" s="57"/>
+      <c r="AA32" s="57">
+        <v>16.600000000000001</v>
+      </c>
       <c r="AB32" s="57"/>
       <c r="AC32" s="57"/>
       <c r="AD32" s="57"/>
@@ -12444,7 +12494,7 @@
       <c r="AI32" s="57"/>
       <c r="AJ32" s="37">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="AK32" s="21">
         <f t="shared" si="1"/>
@@ -12462,11 +12512,11 @@
       </c>
       <c r="AO32" s="23">
         <f t="shared" si="5"/>
-        <v>18.109090909090909</v>
+        <v>18.043478260869566</v>
       </c>
       <c r="AP32" s="23">
         <f t="shared" si="4"/>
-        <v>1.7795531358296586</v>
+        <v>1.7139404876083155</v>
       </c>
     </row>
     <row r="33" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12548,7 +12598,9 @@
       <c r="Z33" s="57">
         <v>16.399999999999999</v>
       </c>
-      <c r="AA33" s="57"/>
+      <c r="AA33" s="57">
+        <v>14.8</v>
+      </c>
       <c r="AB33" s="57"/>
       <c r="AC33" s="57"/>
       <c r="AD33" s="57"/>
@@ -12559,7 +12611,7 @@
       <c r="AI33" s="57"/>
       <c r="AJ33" s="37">
         <f t="shared" si="0"/>
-        <v>16.399999999999999</v>
+        <v>14.8</v>
       </c>
       <c r="AK33" s="21">
         <f t="shared" si="1"/>
@@ -12577,11 +12629,11 @@
       </c>
       <c r="AO33" s="23">
         <f t="shared" si="5"/>
-        <v>15.822727272727271</v>
+        <v>15.778260869565216</v>
       </c>
       <c r="AP33" s="23">
         <f t="shared" si="4"/>
-        <v>1.0781147402838211</v>
+        <v>1.0336483371217664</v>
       </c>
       <c r="AT33" s="15"/>
     </row>
@@ -12715,7 +12767,9 @@
       <c r="Z35" s="57">
         <v>31</v>
       </c>
-      <c r="AA35" s="57"/>
+      <c r="AA35" s="57">
+        <v>29.4</v>
+      </c>
       <c r="AB35" s="57"/>
       <c r="AC35" s="57"/>
       <c r="AD35" s="57"/>
@@ -12726,7 +12780,7 @@
       <c r="AI35" s="57"/>
       <c r="AJ35" s="37">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>29.4</v>
       </c>
       <c r="AK35" s="21">
         <f t="shared" si="1"/>
@@ -12744,11 +12798,11 @@
       </c>
       <c r="AO35" s="23">
         <f>IF(COUNTIF(E35:AI35,"&gt;0")&gt;=15,AVERAGE(E35:AI35),"")</f>
-        <v>31.909090909090903</v>
+        <v>31.799999999999994</v>
       </c>
       <c r="AP35" s="23">
         <f t="shared" si="4"/>
-        <v>0.83639505655634139</v>
+        <v>0.72730414746543204</v>
       </c>
       <c r="AT35" s="15"/>
     </row>
@@ -12951,7 +13005,9 @@
       <c r="Z38" s="57">
         <v>29</v>
       </c>
-      <c r="AA38" s="57"/>
+      <c r="AA38" s="57">
+        <v>29.8</v>
+      </c>
       <c r="AB38" s="57"/>
       <c r="AC38" s="57"/>
       <c r="AD38" s="57"/>
@@ -12962,7 +13018,7 @@
       <c r="AI38" s="57"/>
       <c r="AJ38" s="37">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>29.8</v>
       </c>
       <c r="AK38" s="21">
         <f t="shared" si="1"/>
@@ -12980,11 +13036,11 @@
       </c>
       <c r="AO38" s="23">
         <f>IF(COUNTIF(E38:AI38,"&gt;0")&gt;=15,AVERAGE(E38:AI38),"")</f>
-        <v>30.068181818181813</v>
+        <v>30.056521739130428</v>
       </c>
       <c r="AP38" s="23">
         <f t="shared" si="4"/>
-        <v>3.915559478923214E-2</v>
+        <v>2.7495515737847143E-2</v>
       </c>
       <c r="AT38" s="15"/>
     </row>
@@ -13067,7 +13123,9 @@
       <c r="Z39" s="57">
         <v>32.4</v>
       </c>
-      <c r="AA39" s="57"/>
+      <c r="AA39" s="57">
+        <v>31.2</v>
+      </c>
       <c r="AB39" s="57"/>
       <c r="AC39" s="57"/>
       <c r="AD39" s="57"/>
@@ -13078,7 +13136,7 @@
       <c r="AI39" s="57"/>
       <c r="AJ39" s="37">
         <f t="shared" si="0"/>
-        <v>32.4</v>
+        <v>31.2</v>
       </c>
       <c r="AK39" s="21">
         <f t="shared" si="1"/>
@@ -13096,11 +13154,11 @@
       </c>
       <c r="AO39" s="23">
         <f t="shared" ref="AO39:AO48" si="7">IF(COUNTIF(E39:AI39,"&gt;0")&gt;=15,AVERAGE(E39:AI39),"")</f>
-        <v>31.404545454545453</v>
+        <v>31.395652173913046</v>
       </c>
       <c r="AP39" s="23">
         <f t="shared" si="4"/>
-        <v>0.56141234368153192</v>
+        <v>0.55251906304912524</v>
       </c>
       <c r="AT39" s="15"/>
     </row>
@@ -13183,7 +13241,9 @@
       <c r="Z40" s="57">
         <v>31.4</v>
       </c>
-      <c r="AA40" s="57"/>
+      <c r="AA40" s="57">
+        <v>29.8</v>
+      </c>
       <c r="AB40" s="57"/>
       <c r="AC40" s="57"/>
       <c r="AD40" s="57"/>
@@ -13194,7 +13254,7 @@
       <c r="AI40" s="57"/>
       <c r="AJ40" s="37">
         <f t="shared" si="0"/>
-        <v>31.4</v>
+        <v>29.8</v>
       </c>
       <c r="AK40" s="21">
         <f t="shared" si="1"/>
@@ -13212,11 +13272,11 @@
       </c>
       <c r="AO40" s="23">
         <f t="shared" si="7"/>
-        <v>29.704545454545453</v>
+        <v>29.708695652173912</v>
       </c>
       <c r="AP40" s="23">
         <f t="shared" si="4"/>
-        <v>0.75699706744867257</v>
+        <v>0.76114726507713115</v>
       </c>
       <c r="AT40" s="15"/>
     </row>
@@ -13299,7 +13359,9 @@
       <c r="Z41" s="57">
         <v>32</v>
       </c>
-      <c r="AA41" s="57"/>
+      <c r="AA41" s="57">
+        <v>27.2</v>
+      </c>
       <c r="AB41" s="57"/>
       <c r="AC41" s="57"/>
       <c r="AD41" s="57"/>
@@ -13310,7 +13372,7 @@
       <c r="AI41" s="57"/>
       <c r="AJ41" s="37">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>27.2</v>
       </c>
       <c r="AK41" s="21">
         <f t="shared" si="1"/>
@@ -13328,11 +13390,11 @@
       </c>
       <c r="AO41" s="23">
         <f t="shared" si="7"/>
-        <v>30.527272727272734</v>
+        <v>30.382608695652181</v>
       </c>
       <c r="AP41" s="23">
         <f t="shared" si="4"/>
-        <v>1.1609644835451434</v>
+        <v>1.0163004519245895</v>
       </c>
       <c r="AT41" s="15"/>
     </row>
@@ -13476,7 +13538,9 @@
       <c r="Z43" s="57">
         <v>31.2</v>
       </c>
-      <c r="AA43" s="57"/>
+      <c r="AA43" s="57">
+        <v>32.4</v>
+      </c>
       <c r="AB43" s="57"/>
       <c r="AC43" s="57"/>
       <c r="AD43" s="57"/>
@@ -13487,7 +13551,7 @@
       <c r="AI43" s="57"/>
       <c r="AJ43" s="37">
         <f t="shared" si="0"/>
-        <v>31.2</v>
+        <v>32.4</v>
       </c>
       <c r="AK43" s="21">
         <f t="shared" si="1"/>
@@ -13505,11 +13569,11 @@
       </c>
       <c r="AO43" s="23">
         <f t="shared" si="7"/>
-        <v>30.926315789473687</v>
+        <v>31</v>
       </c>
       <c r="AP43" s="23">
         <f t="shared" si="4"/>
-        <v>0.86525396151669653</v>
+        <v>0.93893817204300944</v>
       </c>
       <c r="AT43" s="15"/>
     </row>
@@ -13590,7 +13654,9 @@
       <c r="Z44" s="29">
         <v>31.2</v>
       </c>
-      <c r="AA44" s="29"/>
+      <c r="AA44" s="29">
+        <v>31.1</v>
+      </c>
       <c r="AB44" s="29"/>
       <c r="AC44" s="29"/>
       <c r="AD44" s="29"/>
@@ -13601,7 +13667,7 @@
       <c r="AI44" s="57"/>
       <c r="AJ44" s="37">
         <f t="shared" si="0"/>
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="AK44" s="21">
         <f t="shared" si="1"/>
@@ -13619,11 +13685,11 @@
       </c>
       <c r="AO44" s="23">
         <f t="shared" si="7"/>
-        <v>31.142857142857139</v>
+        <v>31.140909090909087</v>
       </c>
       <c r="AP44" s="23">
         <f t="shared" si="4"/>
-        <v>2.0996699374966781</v>
+        <v>2.0977218855486264</v>
       </c>
       <c r="AT44" s="15"/>
     </row>
@@ -13706,7 +13772,9 @@
       <c r="Z45" s="57">
         <v>30.4</v>
       </c>
-      <c r="AA45" s="57"/>
+      <c r="AA45" s="57">
+        <v>30.6</v>
+      </c>
       <c r="AB45" s="57"/>
       <c r="AC45" s="57"/>
       <c r="AD45" s="57"/>
@@ -13717,7 +13785,7 @@
       <c r="AI45" s="57"/>
       <c r="AJ45" s="37">
         <f t="shared" si="0"/>
-        <v>30.4</v>
+        <v>30.6</v>
       </c>
       <c r="AK45" s="21">
         <f t="shared" si="1"/>
@@ -13735,11 +13803,11 @@
       </c>
       <c r="AO45" s="23">
         <f t="shared" si="7"/>
-        <v>30.372727272727278</v>
+        <v>30.382608695652181</v>
       </c>
       <c r="AP45" s="23">
         <f t="shared" si="4"/>
-        <v>0.82691087984844813</v>
+        <v>0.83679230277335037</v>
       </c>
       <c r="AT45" s="15"/>
     </row>
@@ -13961,7 +14029,9 @@
       <c r="Z48" s="57">
         <v>32.6</v>
       </c>
-      <c r="AA48" s="57"/>
+      <c r="AA48" s="57">
+        <v>33.200000000000003</v>
+      </c>
       <c r="AB48" s="57"/>
       <c r="AC48" s="57"/>
       <c r="AD48" s="57"/>
@@ -13972,29 +14042,29 @@
       <c r="AI48" s="57"/>
       <c r="AJ48" s="37">
         <f t="shared" si="0"/>
-        <v>32.6</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="AK48" s="21">
         <f t="shared" si="1"/>
-        <v>32.9</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="AL48" s="22">
         <v>35.200000000000003</v>
       </c>
       <c r="AM48" s="23">
         <f t="shared" si="2"/>
-        <v>-2.3000000000000043</v>
+        <v>-2</v>
       </c>
       <c r="AN48" s="23">
         <v>30.34253285543608</v>
       </c>
       <c r="AO48" s="23">
         <f t="shared" si="7"/>
-        <v>30.695454545454542</v>
+        <v>30.804347826086957</v>
       </c>
       <c r="AP48" s="23">
         <f t="shared" si="4"/>
-        <v>0.35292169001846219</v>
+        <v>0.4618149706508774</v>
       </c>
     </row>
     <row r="49" spans="5:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -26893,12 +26963,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
     <mergeCell ref="M1:M2"/>
     <mergeCell ref="N1:N2"/>
     <mergeCell ref="O1:O2"/>
@@ -26908,6 +26972,12 @@
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="L1:L2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:O13 D15:O31 D33:O34 D36:O46">
     <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="equal">
